--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251122_201309.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251122_201309.xlsx
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251122_201309.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251122_201309.xlsx
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
